--- a/asignaciones.xlsx
+++ b/asignaciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Mi unidad\+DOCENCIA\1 GENERAL\pdf_moodle_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90442BF2-B23F-4247-AE41-FD63A78559AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1BDF2E7-3238-4C5A-80AE-17309DABD1C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>matricula</t>
   </si>
@@ -42,9 +42,6 @@
     <t>5-6</t>
   </si>
   <si>
-    <t>7-8</t>
-  </si>
-  <si>
     <t>9-10</t>
   </si>
   <si>
@@ -81,9 +78,6 @@
     <t>31-32</t>
   </si>
   <si>
-    <t>33-34</t>
-  </si>
-  <si>
     <t>202530486</t>
   </si>
   <si>
@@ -130,6 +124,165 @@
   </si>
   <si>
     <t>202530450</t>
+  </si>
+  <si>
+    <t>202530499</t>
+  </si>
+  <si>
+    <t>59-60</t>
+  </si>
+  <si>
+    <t>61-62</t>
+  </si>
+  <si>
+    <t>65-66</t>
+  </si>
+  <si>
+    <t>67-68</t>
+  </si>
+  <si>
+    <t>69-70</t>
+  </si>
+  <si>
+    <t>71-72</t>
+  </si>
+  <si>
+    <t>73-74</t>
+  </si>
+  <si>
+    <t>75-76</t>
+  </si>
+  <si>
+    <t>77-78</t>
+  </si>
+  <si>
+    <t>79-80</t>
+  </si>
+  <si>
+    <t>81-82</t>
+  </si>
+  <si>
+    <t>83-84</t>
+  </si>
+  <si>
+    <t>85-86</t>
+  </si>
+  <si>
+    <t>87-88</t>
+  </si>
+  <si>
+    <t>89-90</t>
+  </si>
+  <si>
+    <t>91-92</t>
+  </si>
+  <si>
+    <t>95-96</t>
+  </si>
+  <si>
+    <t>202530427</t>
+  </si>
+  <si>
+    <t>202530502</t>
+  </si>
+  <si>
+    <t>202530477</t>
+  </si>
+  <si>
+    <t>202510243</t>
+  </si>
+  <si>
+    <t>202530611</t>
+  </si>
+  <si>
+    <t>202530440</t>
+  </si>
+  <si>
+    <t>202530618</t>
+  </si>
+  <si>
+    <t>202530403</t>
+  </si>
+  <si>
+    <t>202530583</t>
+  </si>
+  <si>
+    <t>202530561</t>
+  </si>
+  <si>
+    <t>202530366</t>
+  </si>
+  <si>
+    <t>202530606</t>
+  </si>
+  <si>
+    <t>202530433</t>
+  </si>
+  <si>
+    <t>202530416</t>
+  </si>
+  <si>
+    <t>202530495</t>
+  </si>
+  <si>
+    <t>202530555</t>
+  </si>
+  <si>
+    <t>35-36</t>
+  </si>
+  <si>
+    <t>202530446</t>
+  </si>
+  <si>
+    <t>39-40</t>
+  </si>
+  <si>
+    <t>202530815</t>
+  </si>
+  <si>
+    <t>43-44</t>
+  </si>
+  <si>
+    <t>202530423</t>
+  </si>
+  <si>
+    <t>45-46</t>
+  </si>
+  <si>
+    <t>202530589</t>
+  </si>
+  <si>
+    <t>47-48</t>
+  </si>
+  <si>
+    <t>202530535</t>
+  </si>
+  <si>
+    <t>49-50</t>
+  </si>
+  <si>
+    <t>202530584</t>
+  </si>
+  <si>
+    <t>51-52</t>
+  </si>
+  <si>
+    <t>202530464</t>
+  </si>
+  <si>
+    <t>53-54</t>
+  </si>
+  <si>
+    <t>202530488</t>
+  </si>
+  <si>
+    <t>55-56</t>
+  </si>
+  <si>
+    <t>202530489</t>
+  </si>
+  <si>
+    <t>57-58</t>
   </si>
 </sst>
 </file>
@@ -179,15 +332,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -470,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
@@ -485,146 +635,340 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>202530499</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
+      <c r="A2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>3</v>
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>4</v>
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>5</v>
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>6</v>
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>8</v>
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>10</v>
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>11</v>
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>12</v>
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>14</v>
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>16</v>
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>17</v>
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>18</v>
+        <v>32</v>
+      </c>
+      <c r="B18" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="3"/>
+      <c r="A19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="3"/>
+      <c r="A20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>64</v>
+      </c>
+      <c r="B32" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" t="s">
+        <v>85</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
